--- a/results/all_results_gru.xlsx
+++ b/results/all_results_gru.xlsx
@@ -26,12 +26,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0000FF00"/>
+        <bgColor rgb="0000FF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000070C0"/>
+        <bgColor rgb="000070C0"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +58,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3334,137 +3348,137 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t>2026-05-23_09-33-40</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="B22" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="D22" t="b">
-        <v>1</v>
-      </c>
-      <c r="E22" t="b">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
+      <c r="D22" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F22" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" t="n">
+      <c r="G22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="1" t="n">
         <v>64</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J22" s="1" t="n">
         <v>0.3303785982224717</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K22" s="1" t="n">
         <v>256</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L22" s="1" t="n">
         <v>0.000359283375708533</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M22" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N22" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O22" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="P22" t="n">
+      <c r="P22" s="1" t="n">
         <v>0.4997087457093679</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="Q22" s="1" t="n">
         <v>0.2578836854304978</v>
       </c>
-      <c r="R22" t="n">
+      <c r="R22" s="1" t="n">
         <v>0.9108313869924541</v>
       </c>
-      <c r="S22" t="n">
+      <c r="S22" s="1" t="n">
         <v>0.9120213907966248</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T22" s="1" t="n">
         <v>0.9108313869924541</v>
       </c>
-      <c r="U22" t="n">
+      <c r="U22" s="1" t="n">
         <v>0.910247036995846</v>
       </c>
-      <c r="V22" t="n">
+      <c r="V22" s="1" t="n">
         <v>0.9853038452529996</v>
       </c>
-      <c r="W22" t="n">
+      <c r="W22" s="1" t="n">
         <v>0.4997087457093679</v>
       </c>
-      <c r="X22" t="n">
+      <c r="X22" s="1" t="n">
         <v>0.8858803812716036</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="Y22" s="1" t="n">
         <v>0.8910167078270816</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="Z22" s="1" t="n">
         <v>0.8858803812716036</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AA22" s="1" t="n">
         <v>0.8790904014459435</v>
       </c>
-      <c r="AB22" t="n">
+      <c r="AB22" s="1" t="n">
         <v>0.9726335337190269</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AC22" s="1" t="n">
         <v>0.1876071439497973</v>
       </c>
-      <c r="AD22" t="n">
+      <c r="AD22" s="1" t="n">
         <v>0.9410809678433015</v>
       </c>
-      <c r="AE22" t="n">
+      <c r="AE22" s="1" t="n">
         <v>0.9405935332692268</v>
       </c>
-      <c r="AF22" t="n">
+      <c r="AF22" s="1" t="n">
         <v>0.9410809678433015</v>
       </c>
-      <c r="AG22" t="n">
+      <c r="AG22" s="1" t="n">
         <v>0.9397145057107308</v>
       </c>
-      <c r="AH22" t="n">
+      <c r="AH22" s="1" t="n">
         <v>0.9937007723426952</v>
       </c>
-      <c r="AI22" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ22" t="n">
+      <c r="AI22" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ22" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AK22" t="n">
+      <c r="AK22" s="1" t="n">
         <v>58.63600616400072</v>
       </c>
-      <c r="AL22" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM22" t="inlineStr">
+      <c r="AL22" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM22" s="1" t="inlineStr">
         <is>
           <t>NVIDIA GeForce RTX 5060</t>
         </is>
       </c>
-      <c r="AN22" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO22" t="n">
+      <c r="AN22" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO22" s="1" t="n">
         <v>92000</v>
       </c>
-      <c r="AP22" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ22" t="b">
+      <c r="AP22" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ22" s="1" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4414,137 +4428,137 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>2026-05-23_09-55-28</t>
         </is>
       </c>
-      <c r="B30" t="n">
+      <c r="B30" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C30" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="D30" t="b">
-        <v>1</v>
-      </c>
-      <c r="E30" t="b">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
+      <c r="D30" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" t="n">
+      <c r="G30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="J30" t="n">
+      <c r="J30" s="2" t="n">
         <v>0.2695420194232719</v>
       </c>
-      <c r="K30" t="n">
+      <c r="K30" s="2" t="n">
         <v>128</v>
       </c>
-      <c r="L30" t="n">
+      <c r="L30" s="2" t="n">
         <v>0.0008714939539565855</v>
       </c>
-      <c r="M30" t="n">
+      <c r="M30" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="N30" t="n">
+      <c r="N30" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="O30" t="n">
+      <c r="O30" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="P30" t="n">
+      <c r="P30" s="2" t="n">
         <v>0.4922862588064094</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="Q30" s="2" t="n">
         <v>0.2783169386268151</v>
       </c>
-      <c r="R30" t="n">
+      <c r="R30" s="2" t="n">
         <v>0.9071801493291416</v>
       </c>
-      <c r="S30" t="n">
+      <c r="S30" s="2" t="n">
         <v>0.9117776366058149</v>
       </c>
-      <c r="T30" t="n">
+      <c r="T30" s="2" t="n">
         <v>0.9071801493291416</v>
       </c>
-      <c r="U30" t="n">
+      <c r="U30" s="2" t="n">
         <v>0.9061096166119763</v>
       </c>
-      <c r="V30" t="n">
+      <c r="V30" s="2" t="n">
         <v>0.9848254134817815</v>
       </c>
-      <c r="W30" t="n">
+      <c r="W30" s="2" t="n">
         <v>0.4922862588064094</v>
       </c>
-      <c r="X30" t="n">
+      <c r="X30" s="2" t="n">
         <v>0.8947313292133654</v>
       </c>
-      <c r="Y30" t="n">
+      <c r="Y30" s="2" t="n">
         <v>0.8969264131354789</v>
       </c>
-      <c r="Z30" t="n">
+      <c r="Z30" s="2" t="n">
         <v>0.8947313292133654</v>
       </c>
-      <c r="AA30" t="n">
+      <c r="AA30" s="2" t="n">
         <v>0.8883839809334979</v>
       </c>
-      <c r="AB30" t="n">
+      <c r="AB30" s="2" t="n">
         <v>0.9673276142706154</v>
       </c>
-      <c r="AC30" t="n">
+      <c r="AC30" s="2" t="n">
         <v>0.2094477307891044</v>
       </c>
-      <c r="AD30" t="n">
+      <c r="AD30" s="2" t="n">
         <v>0.9359484654865403</v>
       </c>
-      <c r="AE30" t="n">
+      <c r="AE30" s="2" t="n">
         <v>0.9374885792538419</v>
       </c>
-      <c r="AF30" t="n">
+      <c r="AF30" s="2" t="n">
         <v>0.9359484654865403</v>
       </c>
-      <c r="AG30" t="n">
+      <c r="AG30" s="2" t="n">
         <v>0.9348594081411752</v>
       </c>
-      <c r="AH30" t="n">
+      <c r="AH30" s="2" t="n">
         <v>0.9913398004557837</v>
       </c>
-      <c r="AI30" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ30" t="n">
+      <c r="AI30" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ30" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="AK30" t="n">
+      <c r="AK30" s="2" t="n">
         <v>88.99320986300154</v>
       </c>
-      <c r="AL30" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM30" t="inlineStr">
+      <c r="AL30" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM30" s="2" t="inlineStr">
         <is>
           <t>NVIDIA GeForce RTX 5060</t>
         </is>
       </c>
-      <c r="AN30" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO30" t="n">
+      <c r="AN30" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO30" s="2" t="n">
         <v>92000</v>
       </c>
-      <c r="AP30" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ30" t="b">
+      <c r="AP30" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ30" s="2" t="b">
         <v>0</v>
       </c>
     </row>

--- a/results/all_results_gru.xlsx
+++ b/results/all_results_gru.xlsx
@@ -26,24 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0000FF00"/>
-        <bgColor rgb="0000FF00"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="000070C0"/>
-        <bgColor rgb="000070C0"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -58,10 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ31"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -646,6 +632,51 @@
           <t>cudnn_benchmark</t>
         </is>
       </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>train_macro_precision</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>train_macro_recall</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>train_macro_f1</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>val_macro_precision</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>val_macro_recall</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>val_macro_f1</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>test_macro_precision</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>test_macro_recall</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>test_macro_f1</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -781,6 +812,33 @@
       <c r="AQ2" t="b">
         <v>0</v>
       </c>
+      <c r="AR2" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0.86</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -916,6 +974,33 @@
       <c r="AQ3" t="b">
         <v>0</v>
       </c>
+      <c r="AR3" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0.83</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1051,6 +1136,33 @@
       <c r="AQ4" t="b">
         <v>0</v>
       </c>
+      <c r="AR4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0.77</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1186,6 +1298,33 @@
       <c r="AQ5" t="b">
         <v>0</v>
       </c>
+      <c r="AR5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.87</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1321,6 +1460,33 @@
       <c r="AQ6" t="b">
         <v>0</v>
       </c>
+      <c r="AR6" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0.83</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1456,6 +1622,33 @@
       <c r="AQ7" t="b">
         <v>0</v>
       </c>
+      <c r="AR7" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0.71</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1591,6 +1784,33 @@
       <c r="AQ8" t="b">
         <v>0</v>
       </c>
+      <c r="AR8" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0.71</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1726,6 +1946,33 @@
       <c r="AQ9" t="b">
         <v>0</v>
       </c>
+      <c r="AR9" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0.72</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1861,6 +2108,33 @@
       <c r="AQ10" t="b">
         <v>0</v>
       </c>
+      <c r="AR10" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0.85</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1996,6 +2270,33 @@
       <c r="AQ11" t="b">
         <v>0</v>
       </c>
+      <c r="AR11" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.86</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2131,6 +2432,33 @@
       <c r="AQ12" t="b">
         <v>0</v>
       </c>
+      <c r="AR12" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0.47</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2266,6 +2594,33 @@
       <c r="AQ13" t="b">
         <v>0</v>
       </c>
+      <c r="AR13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2401,6 +2756,33 @@
       <c r="AQ14" t="b">
         <v>0</v>
       </c>
+      <c r="AR14" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2536,6 +2918,33 @@
       <c r="AQ15" t="b">
         <v>0</v>
       </c>
+      <c r="AR15" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0.85</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2671,6 +3080,33 @@
       <c r="AQ16" t="b">
         <v>0</v>
       </c>
+      <c r="AR16" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0.87</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2806,6 +3242,33 @@
       <c r="AQ17" t="b">
         <v>0</v>
       </c>
+      <c r="AR17" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0.78</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2941,6 +3404,33 @@
       <c r="AQ18" t="b">
         <v>0</v>
       </c>
+      <c r="AR18" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0.65</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3076,6 +3566,33 @@
       <c r="AQ19" t="b">
         <v>0</v>
       </c>
+      <c r="AR19" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0.89</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3211,6 +3728,33 @@
       <c r="AQ20" t="b">
         <v>0</v>
       </c>
+      <c r="AR20" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0.87</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3346,140 +3890,194 @@
       <c r="AQ21" t="b">
         <v>0</v>
       </c>
+      <c r="AR21" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0.89</v>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>2026-05-23_09-33-40</t>
         </is>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" t="n">
         <v>100</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" t="n">
         <v>42</v>
       </c>
-      <c r="D22" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="E22" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F22" s="1" t="n">
+      <c r="D22" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" t="b">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
         <v>8</v>
       </c>
-      <c r="G22" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" s="1" t="n">
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
         <v>64</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" t="n">
         <v>0.3303785982224717</v>
       </c>
-      <c r="K22" s="1" t="n">
+      <c r="K22" t="n">
         <v>256</v>
       </c>
-      <c r="L22" s="1" t="n">
+      <c r="L22" t="n">
         <v>0.000359283375708533</v>
       </c>
-      <c r="M22" s="1" t="n">
+      <c r="M22" t="n">
         <v>50</v>
       </c>
-      <c r="N22" s="1" t="n">
+      <c r="N22" t="n">
         <v>4</v>
       </c>
-      <c r="O22" s="1" t="n">
+      <c r="O22" t="n">
         <v>2</v>
       </c>
-      <c r="P22" s="1" t="n">
+      <c r="P22" t="n">
         <v>0.4997087457093679</v>
       </c>
-      <c r="Q22" s="1" t="n">
+      <c r="Q22" t="n">
         <v>0.2578836854304978</v>
       </c>
-      <c r="R22" s="1" t="n">
+      <c r="R22" t="n">
         <v>0.9108313869924541</v>
       </c>
-      <c r="S22" s="1" t="n">
+      <c r="S22" t="n">
         <v>0.9120213907966248</v>
       </c>
-      <c r="T22" s="1" t="n">
+      <c r="T22" t="n">
         <v>0.9108313869924541</v>
       </c>
-      <c r="U22" s="1" t="n">
+      <c r="U22" t="n">
         <v>0.910247036995846</v>
       </c>
-      <c r="V22" s="1" t="n">
+      <c r="V22" t="n">
         <v>0.9853038452529996</v>
       </c>
-      <c r="W22" s="1" t="n">
+      <c r="W22" t="n">
         <v>0.4997087457093679</v>
       </c>
-      <c r="X22" s="1" t="n">
+      <c r="X22" t="n">
         <v>0.8858803812716036</v>
       </c>
-      <c r="Y22" s="1" t="n">
+      <c r="Y22" t="n">
         <v>0.8910167078270816</v>
       </c>
-      <c r="Z22" s="1" t="n">
+      <c r="Z22" t="n">
         <v>0.8858803812716036</v>
       </c>
-      <c r="AA22" s="1" t="n">
+      <c r="AA22" t="n">
         <v>0.8790904014459435</v>
       </c>
-      <c r="AB22" s="1" t="n">
+      <c r="AB22" t="n">
         <v>0.9726335337190269</v>
       </c>
-      <c r="AC22" s="1" t="n">
+      <c r="AC22" t="n">
         <v>0.1876071439497973</v>
       </c>
-      <c r="AD22" s="1" t="n">
+      <c r="AD22" t="n">
         <v>0.9410809678433015</v>
       </c>
-      <c r="AE22" s="1" t="n">
+      <c r="AE22" t="n">
         <v>0.9405935332692268</v>
       </c>
-      <c r="AF22" s="1" t="n">
+      <c r="AF22" t="n">
         <v>0.9410809678433015</v>
       </c>
-      <c r="AG22" s="1" t="n">
+      <c r="AG22" t="n">
         <v>0.9397145057107308</v>
       </c>
-      <c r="AH22" s="1" t="n">
+      <c r="AH22" t="n">
         <v>0.9937007723426952</v>
       </c>
-      <c r="AI22" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ22" s="1" t="n">
+      <c r="AI22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ22" t="n">
         <v>10</v>
       </c>
-      <c r="AK22" s="1" t="n">
+      <c r="AK22" t="n">
         <v>58.63600616400072</v>
       </c>
-      <c r="AL22" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM22" s="1" t="inlineStr">
+      <c r="AL22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM22" t="inlineStr">
         <is>
           <t>NVIDIA GeForce RTX 5060</t>
         </is>
       </c>
-      <c r="AN22" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO22" s="1" t="n">
+      <c r="AN22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO22" t="n">
         <v>92000</v>
       </c>
-      <c r="AP22" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ22" s="1" t="b">
-        <v>0</v>
+      <c r="AP22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0.89</v>
       </c>
     </row>
     <row r="23">
@@ -3616,6 +4214,33 @@
       <c r="AQ23" t="b">
         <v>0</v>
       </c>
+      <c r="AR23" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0.82</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3751,6 +4376,33 @@
       <c r="AQ24" t="b">
         <v>0</v>
       </c>
+      <c r="AR24" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3886,6 +4538,33 @@
       <c r="AQ25" t="b">
         <v>0</v>
       </c>
+      <c r="AR25" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0.78</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4021,6 +4700,33 @@
       <c r="AQ26" t="b">
         <v>0</v>
       </c>
+      <c r="AR26" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0.71</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4156,6 +4862,33 @@
       <c r="AQ27" t="b">
         <v>0</v>
       </c>
+      <c r="AR27" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0.73</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4291,6 +5024,33 @@
       <c r="AQ28" t="b">
         <v>0</v>
       </c>
+      <c r="AR28" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0.85</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4426,140 +5186,194 @@
       <c r="AQ29" t="b">
         <v>0</v>
       </c>
+      <c r="AR29" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>0.88</v>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>2026-05-23_09-55-28</t>
         </is>
       </c>
-      <c r="B30" s="2" t="n">
+      <c r="B30" t="n">
         <v>100</v>
       </c>
-      <c r="C30" s="2" t="n">
+      <c r="C30" t="n">
         <v>42</v>
       </c>
-      <c r="D30" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E30" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F30" s="2" t="n">
+      <c r="D30" t="b">
+        <v>1</v>
+      </c>
+      <c r="E30" t="b">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
         <v>8</v>
       </c>
-      <c r="G30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" s="2" t="n">
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
         <v>16</v>
       </c>
-      <c r="J30" s="2" t="n">
+      <c r="J30" t="n">
         <v>0.2695420194232719</v>
       </c>
-      <c r="K30" s="2" t="n">
+      <c r="K30" t="n">
         <v>128</v>
       </c>
-      <c r="L30" s="2" t="n">
+      <c r="L30" t="n">
         <v>0.0008714939539565855</v>
       </c>
-      <c r="M30" s="2" t="n">
+      <c r="M30" t="n">
         <v>41</v>
       </c>
-      <c r="N30" s="2" t="n">
+      <c r="N30" t="n">
         <v>2</v>
       </c>
-      <c r="O30" s="2" t="n">
+      <c r="O30" t="n">
         <v>2</v>
       </c>
-      <c r="P30" s="2" t="n">
+      <c r="P30" t="n">
         <v>0.4922862588064094</v>
       </c>
-      <c r="Q30" s="2" t="n">
+      <c r="Q30" t="n">
         <v>0.2783169386268151</v>
       </c>
-      <c r="R30" s="2" t="n">
+      <c r="R30" t="n">
         <v>0.9071801493291416</v>
       </c>
-      <c r="S30" s="2" t="n">
+      <c r="S30" t="n">
         <v>0.9117776366058149</v>
       </c>
-      <c r="T30" s="2" t="n">
+      <c r="T30" t="n">
         <v>0.9071801493291416</v>
       </c>
-      <c r="U30" s="2" t="n">
+      <c r="U30" t="n">
         <v>0.9061096166119763</v>
       </c>
-      <c r="V30" s="2" t="n">
+      <c r="V30" t="n">
         <v>0.9848254134817815</v>
       </c>
-      <c r="W30" s="2" t="n">
+      <c r="W30" t="n">
         <v>0.4922862588064094</v>
       </c>
-      <c r="X30" s="2" t="n">
+      <c r="X30" t="n">
         <v>0.8947313292133654</v>
       </c>
-      <c r="Y30" s="2" t="n">
+      <c r="Y30" t="n">
         <v>0.8969264131354789</v>
       </c>
-      <c r="Z30" s="2" t="n">
+      <c r="Z30" t="n">
         <v>0.8947313292133654</v>
       </c>
-      <c r="AA30" s="2" t="n">
+      <c r="AA30" t="n">
         <v>0.8883839809334979</v>
       </c>
-      <c r="AB30" s="2" t="n">
+      <c r="AB30" t="n">
         <v>0.9673276142706154</v>
       </c>
-      <c r="AC30" s="2" t="n">
+      <c r="AC30" t="n">
         <v>0.2094477307891044</v>
       </c>
-      <c r="AD30" s="2" t="n">
+      <c r="AD30" t="n">
         <v>0.9359484654865403</v>
       </c>
-      <c r="AE30" s="2" t="n">
+      <c r="AE30" t="n">
         <v>0.9374885792538419</v>
       </c>
-      <c r="AF30" s="2" t="n">
+      <c r="AF30" t="n">
         <v>0.9359484654865403</v>
       </c>
-      <c r="AG30" s="2" t="n">
+      <c r="AG30" t="n">
         <v>0.9348594081411752</v>
       </c>
-      <c r="AH30" s="2" t="n">
+      <c r="AH30" t="n">
         <v>0.9913398004557837</v>
       </c>
-      <c r="AI30" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ30" s="2" t="n">
+      <c r="AI30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ30" t="n">
         <v>10</v>
       </c>
-      <c r="AK30" s="2" t="n">
+      <c r="AK30" t="n">
         <v>88.99320986300154</v>
       </c>
-      <c r="AL30" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM30" s="2" t="inlineStr">
+      <c r="AL30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM30" t="inlineStr">
         <is>
           <t>NVIDIA GeForce RTX 5060</t>
         </is>
       </c>
-      <c r="AN30" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO30" s="2" t="n">
+      <c r="AN30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO30" t="n">
         <v>92000</v>
       </c>
-      <c r="AP30" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ30" s="2" t="b">
-        <v>0</v>
+      <c r="AP30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0.87</v>
       </c>
     </row>
     <row r="31">
@@ -4695,6 +5509,33 @@
       </c>
       <c r="AQ31" t="b">
         <v>0</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0.88</v>
       </c>
     </row>
   </sheetData>
